--- a/docs/산출물/07_한결공조_AS관리_단위테스트시나리오_V1.0.xlsx
+++ b/docs/산출물/07_한결공조_AS관리_단위테스트시나리오_V1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\my-first-project\docs\산출물\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72666BFF-5093-4D89-AAE6-1B989F88EDAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{593270B5-9334-4265-9325-D840CAF876D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3315,19 +3315,19 @@
     <t>출동 승인 요청</t>
   </si>
   <si>
-    <t>협력 기사 화면에 [승인 요청] 빠른 작업이 보이지 않음 → 기사 권한 집합에 Flow 실행 권한 없음으로 추정</t>
+    <t>협력 기사 화면에 [승인 요청] 빠른 작업이 보이지 않음 → 원인: 출동 피드 추적이 켜져 빠른 작업이 Chatter 게시자 영역에 배치됐는데 출동 레코드 페이지에 피드 구성 요소가 없음. 강조 표시 패널을 동적 작업으로 전환(편집·승인 요청·소유자 변경·복제·삭제)</t>
+  </si>
+  <si>
+    <t>처음 추정(Flow 실행 권한)은 원인 아님. 최민호 화면 확인</t>
+  </si>
+  <si>
+    <t>사용 부품 삭제</t>
+  </si>
+  <si>
+    <t>삭제 시 표준과 Apex가 모두 재고를 되돌려 이중 증가(R6) → Apex 되돌림 제거 결정</t>
   </si>
   <si>
     <t>진행 중</t>
-  </si>
-  <si>
-    <t>해결 방법(Run Flows 추가 / Flow User) 결정 대기</t>
-  </si>
-  <si>
-    <t>사용 부품 삭제</t>
-  </si>
-  <si>
-    <t>삭제 시 표준과 Apex가 모두 재고를 되돌려 이중 증가(R6) → Apex 되돌림 제거 결정</t>
   </si>
   <si>
     <t>코드 반영 대기</t>
@@ -4389,7 +4389,7 @@
         <xdr:cNvPr id="3" name="그림 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C7EB983-014C-0A26-5383-5B78ABF3E44F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A119842-A72D-99B7-7C0B-101DF5DA8D51}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5035,10 +5035,10 @@
         <v>9</v>
       </c>
       <c r="E29" s="31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F29" s="43">
-        <v>0.88888888888888895</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5587,7 +5587,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="23" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" s="23" customFormat="1" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A14" s="48">
         <v>11</v>
       </c>
@@ -5609,13 +5609,17 @@
       <c r="G14" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
+      <c r="H14" s="49">
+        <v>46311</v>
+      </c>
+      <c r="I14" s="49">
+        <v>46311</v>
+      </c>
       <c r="J14" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="K14" s="48" t="s">
         <v>1081</v>
-      </c>
-      <c r="K14" s="48" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="23" customFormat="1" ht="27" x14ac:dyDescent="0.3">
@@ -5623,10 +5627,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="16" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>1083</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>1084</v>
       </c>
       <c r="D15" s="16" t="s">
         <v>1061</v>
@@ -5643,7 +5647,7 @@
       <c r="H15" s="50"/>
       <c r="I15" s="50"/>
       <c r="J15" s="16" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>1085</v>
@@ -6272,7 +6276,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51B07AF2-70F3-4B52-B36C-7E5E7ACD62FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CE05D1B-E7B4-42AC-B0C1-3272028EBEFB}">
   <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6760,7 +6764,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F3E27C0-1ADD-4B09-96AC-3C89B88CD06B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB2DF960-80BF-4F95-B8AE-F35E2782DCDF}">
   <dimension ref="A1:L200"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10685,7 +10689,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4:J16" xr:uid="{545A77F4-78EB-4EAA-87E2-98AEE095EAFB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4:J16" xr:uid="{02581B8D-C45A-4592-BE36-3E7BF2B19DBE}">
       <formula1>진행결과</formula1>
     </dataValidation>
   </dataValidations>
@@ -10695,7 +10699,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AAFCD86-69CF-4A2A-838C-4EEB694D9D06}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{166BFA2C-C790-4BA7-8788-0023858C9002}">
   <dimension ref="A1:L200"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14164,7 +14168,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4:J16" xr:uid="{E284B537-1923-4735-B680-DC5EE8D04F7C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4:J16" xr:uid="{A358E477-FE59-4915-96D0-6D7B6AB625C8}">
       <formula1>진행결과</formula1>
     </dataValidation>
   </dataValidations>
@@ -14174,7 +14178,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D54F1B2-656A-48D0-A1FB-A9A170A14FA3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B70BFD37-5B9E-4AC3-9A34-4FF33D603216}">
   <dimension ref="A1:L200"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17883,7 +17887,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4:J16" xr:uid="{1869C861-1D20-436D-B775-07EA195F1C48}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4:J16" xr:uid="{4EE87E8F-06B9-4C53-952E-3B042FD4E78C}">
       <formula1>진행결과</formula1>
     </dataValidation>
   </dataValidations>
@@ -17893,7 +17897,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F869AF-1A02-4295-9791-2A2A25293B60}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16C4D88B-74F5-4204-9B53-1007CCB5EE2A}">
   <dimension ref="A1:L200"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -21554,7 +21558,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4:J16" xr:uid="{ADF1A296-E9EC-43FA-91E0-3F1EE274CDCB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4:J16" xr:uid="{05EC11ED-2486-473B-B246-A971CCF6962A}">
       <formula1>진행결과</formula1>
     </dataValidation>
   </dataValidations>
@@ -21564,7 +21568,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{428E5EAB-DB3D-4E3D-B0D9-2D7E93D8CBB3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A63E2B43-2EC4-4619-8165-01CA939F24CB}">
   <dimension ref="A1:L200"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -25705,7 +25709,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4:J16" xr:uid="{7FD82CD2-AB12-4681-997F-640C1E1E5DEA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4:J16" xr:uid="{48EA9C12-066B-4CBD-9794-07C6244609E1}">
       <formula1>진행결과</formula1>
     </dataValidation>
   </dataValidations>
@@ -25715,7 +25719,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{569B5DE1-1745-48CA-BC4D-301505F075BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F3AD0B7-89C5-47DB-AC49-F813D16E8D4E}">
   <dimension ref="A1:L200"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -28656,7 +28660,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4:J6" xr:uid="{76C0095C-FAF2-478C-9959-5474F4EFE94B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4:J6" xr:uid="{85039BCA-17EC-4856-B3B0-DBE2D9C98BED}">
       <formula1>진행결과</formula1>
     </dataValidation>
   </dataValidations>
